--- a/analise_eua/semicondutores/nvidia/nvda_10q.xlsx
+++ b/analise_eua/semicondutores/nvidia/nvda_10q.xlsx
@@ -434,65 +434,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T31"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46138</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45956</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45865</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45774</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45592</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45501</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45410</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45228</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45137</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45046</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44864</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44773</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44682</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44500</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44409</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44318</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44129</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44038</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43947</v>
       </c>
     </row>
@@ -503,60 +506,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>22443</v>
+      </c>
+      <c r="C2" t="n">
         <v>13237</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>11486</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>11639</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>15234</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>9107</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>8563</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>7587</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>5519</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>5783</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>5079</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>2800</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>3013</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>3887</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>1288</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>5628</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>978</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>2251</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>3274</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>15494</v>
       </c>
     </row>
@@ -567,11 +573,11 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>34143</v>
+      </c>
+      <c r="C3" t="n">
         <v>37098</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
@@ -621,6 +627,9 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -631,11 +640,11 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>42783</v>
+      </c>
+      <c r="C4" t="n">
         <v>30237</v>
       </c>
-      <c r="C4" t="n">
-        <v>0</v>
-      </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
@@ -685,6 +694,9 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -695,60 +707,63 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>63059</v>
+      </c>
+      <c r="C5" t="n">
         <v>40710</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>33391</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>27808</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>22132</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>17693</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>14132</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>12365</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>8309</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>7066</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>4080</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>4908</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>5317</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>5438</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3954</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>3586</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>3024</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>2546</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>2084</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>1907</v>
       </c>
     </row>
@@ -759,60 +774,63 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>31575</v>
+      </c>
+      <c r="C6" t="n">
         <v>25797</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>19784</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>14962</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>11333</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>7654</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>6675</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>5864</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>4779</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>4319</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>4611</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>4454</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>3889</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>3163</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>2233</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>2114</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>1992</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>1495</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>1401</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>1128</v>
       </c>
     </row>
@@ -823,60 +841,63 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>3409</v>
+      </c>
+      <c r="C7" t="n">
         <v>3916</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>2709</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>2658</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>2779</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>3806</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>4026</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>4062</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>1289</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>1389</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>872</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>718</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>1175</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>636</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>321</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>452</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>444</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>213</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>215</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>195</v>
       </c>
     </row>
@@ -887,60 +908,63 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>197412</v>
+      </c>
+      <c r="C8" t="n">
         <v>150995</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>116492</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>102219</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>89935</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>67640</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>59633</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>53729</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>32658</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>28797</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>24883</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>23223</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>27418</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>29575</v>
-      </c>
-      <c r="O8" t="n">
-        <v>25806</v>
       </c>
       <c r="P8" t="n">
         <v>25806</v>
       </c>
       <c r="Q8" t="n">
+        <v>25806</v>
+      </c>
+      <c r="R8" t="n">
         <v>18127</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>14393</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>14681</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>19584</v>
       </c>
     </row>
@@ -951,60 +975,63 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>14285</v>
+      </c>
+      <c r="C9" t="n">
         <v>12403</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>9780</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>9141</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>7136</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>5343</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>4885</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>4006</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>3844</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>3799</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>3740</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>3774</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>3233</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>2916</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>2509</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>2364</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>2268</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>2059</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>1964</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>1715</v>
       </c>
     </row>
@@ -1015,60 +1042,63 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>5390</v>
+      </c>
+      <c r="C10" t="n">
         <v>4258</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>2281</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>2084</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>1810</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>1755</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>1556</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>1532</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>1316</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>1235</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>1094</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>927</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>852</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>856</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>830</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>801</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>727</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>681</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>701</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>595</v>
       </c>
     </row>
@@ -1079,28 +1109,28 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>21125</v>
+      </c>
+      <c r="C11" t="n">
         <v>20894</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>6261</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>5755</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>5498</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>4724</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>4622</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>4453</v>
-      </c>
-      <c r="I11" t="n">
-        <v>4430</v>
       </c>
       <c r="J11" t="n">
         <v>4430</v>
@@ -1109,19 +1139,19 @@
         <v>4430</v>
       </c>
       <c r="L11" t="n">
-        <v>4372</v>
+        <v>4430</v>
       </c>
       <c r="M11" t="n">
         <v>4372</v>
       </c>
       <c r="N11" t="n">
+        <v>4372</v>
+      </c>
+      <c r="O11" t="n">
         <v>4365</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>4302</v>
-      </c>
-      <c r="P11" t="n">
-        <v>4193</v>
       </c>
       <c r="Q11" t="n">
         <v>4193</v>
@@ -1133,6 +1163,9 @@
         <v>4193</v>
       </c>
       <c r="T11" t="n">
+        <v>4193</v>
+      </c>
+      <c r="U11" t="n">
         <v>628</v>
       </c>
     </row>
@@ -1143,60 +1176,63 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>2998</v>
+      </c>
+      <c r="C12" t="n">
         <v>3120</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>936</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>755</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>769</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>838</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>952</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>986</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>1251</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>1395</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>1541</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>1850</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>2036</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>2211</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>2454</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>2478</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>2613</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>2861</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>2854</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>80</v>
       </c>
     </row>
@@ -1207,60 +1243,63 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>12159</v>
+      </c>
+      <c r="C13" t="n">
         <v>11707</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>13674</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>13570</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>13318</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>10276</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>9578</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>7798</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>5982</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>5398</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>4568</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>2762</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>2225</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>1784</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>970</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>958</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>778</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>666</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>630</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>533</v>
       </c>
     </row>
@@ -1271,11 +1310,11 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>51157</v>
+      </c>
+      <c r="C14" t="n">
         <v>43364</v>
       </c>
-      <c r="C14" t="n">
-        <v>0</v>
-      </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
@@ -1325,6 +1364,9 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1335,60 +1377,63 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>15746</v>
+      </c>
+      <c r="C15" t="n">
         <v>12733</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>11724</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>7216</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>6788</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>5437</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>4001</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>4568</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>4667</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>4501</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>4204</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>3580</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>3340</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>3505</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>3761</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>2050</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>2090</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>2028</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>157</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>119</v>
       </c>
     </row>
@@ -1399,60 +1444,63 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>320272</v>
+      </c>
+      <c r="C16" t="n">
         <v>259474</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>161148</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>140740</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>125254</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>96013</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>85227</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>77072</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>54148</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>49555</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>44460</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>40488</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>43476</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>45212</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>40632</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>38650</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>30796</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>26881</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>25180</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>23254</v>
       </c>
     </row>
@@ -1463,60 +1511,63 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>15059</v>
+      </c>
+      <c r="C17" t="n">
         <v>13097</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>8624</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>9064</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>7331</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>5353</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>3680</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>2715</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>2380</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>1929</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>1141</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>1491</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>2421</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>1999</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>1664</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>1474</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>1218</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>1097</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>893</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>761</v>
       </c>
     </row>
@@ -1527,60 +1578,63 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>26960</v>
+      </c>
+      <c r="C18" t="n">
         <v>29787</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>16452</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>15193</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>19211</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>11126</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>10289</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>11258</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>5472</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>7156</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>4869</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>4115</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>3903</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>3563</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>1948</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>1974</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>1787</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>1574</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>1517</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>1142</v>
       </c>
     </row>
@@ -1594,11 +1648,11 @@
         <v>1000</v>
       </c>
       <c r="C19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D19" t="n">
         <v>999</v>
       </c>
-      <c r="D19" t="n">
-        <v>0</v>
-      </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
@@ -1609,42 +1663,45 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>1250</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1249</v>
       </c>
       <c r="J19" t="n">
         <v>1249</v>
       </c>
       <c r="K19" t="n">
+        <v>1249</v>
+      </c>
+      <c r="L19" t="n">
         <v>1250</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1249</v>
       </c>
       <c r="M19" t="n">
         <v>1249</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1249</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
         <v>1000</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>999</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>998</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
       <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1655,60 +1712,63 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>43019</v>
+      </c>
+      <c r="C20" t="n">
         <v>43884</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>26075</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>24257</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>26542</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>16479</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>13969</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>15223</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>9101</v>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>10334</v>
       </c>
-      <c r="K20" t="n">
+      <c r="L20" t="n">
         <v>7260</v>
       </c>
-      <c r="L20" t="n">
+      <c r="M20" t="n">
         <v>6855</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>7573</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>5562</v>
       </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
         <v>3612</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
         <v>4448</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>4004</v>
       </c>
-      <c r="R20" t="n">
+      <c r="S20" t="n">
         <v>3669</v>
       </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
         <v>2410</v>
       </c>
-      <c r="T20" t="n">
+      <c r="U20" t="n">
         <v>1903</v>
       </c>
     </row>
@@ -1719,60 +1779,63 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>32366</v>
+      </c>
+      <c r="C21" t="n">
         <v>7470</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>7468</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>8466</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>8464</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>8462</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>8461</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>8460</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>8457</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>8456</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>9704</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>9701</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>9700</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>10947</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>10944</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>10943</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>5964</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>5963</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>6960</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>6959</v>
       </c>
     </row>
@@ -1783,60 +1846,63 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>4985</v>
+      </c>
+      <c r="C22" t="n">
         <v>3878</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>2014</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>1831</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>1521</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>1490</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>1304</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>1281</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>1091</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>1041</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>939</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>798</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>743</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>752</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>743</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>716</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>640</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>604</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>611</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>519</v>
       </c>
     </row>
@@ -1847,60 +1913,63 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>10918</v>
+      </c>
+      <c r="C23" t="n">
         <v>8768</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>6694</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>6055</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>4884</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>3683</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>3336</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>2966</v>
       </c>
-      <c r="I23" t="n">
+      <c r="J23" t="n">
         <v>2234</v>
       </c>
-      <c r="J23" t="n">
+      <c r="K23" t="n">
         <v>2223</v>
       </c>
-      <c r="K23" t="n">
+      <c r="L23" t="n">
         <v>2037</v>
       </c>
-      <c r="L23" t="n">
+      <c r="M23" t="n">
         <v>1785</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>1609</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>1631</v>
       </c>
-      <c r="O23" t="n">
+      <c r="P23" t="n">
         <v>1535</v>
       </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
         <v>1396</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="R23" t="n">
         <v>1414</v>
       </c>
-      <c r="R23" t="n">
+      <c r="S23" t="n">
         <v>1311</v>
       </c>
-      <c r="S23" t="n">
+      <c r="T23" t="n">
         <v>1285</v>
       </c>
-      <c r="T23" t="n">
+      <c r="U23" t="n">
         <v>774</v>
       </c>
     </row>
@@ -1911,60 +1980,63 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>91288</v>
+      </c>
+      <c r="C24" t="n">
         <v>64000</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>42251</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>40609</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>41411</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>30114</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>27070</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>27930</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>20883</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>22054</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>19940</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>19139</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>19625</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>18892</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>16834</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>17503</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>12022</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>11547</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>11266</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>10155</v>
       </c>
     </row>
@@ -1987,13 +2059,13 @@
         <v>24</v>
       </c>
       <c r="F25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G25" t="n">
         <v>25</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I25" t="n">
         <v>2</v>
@@ -2011,7 +2083,7 @@
         <v>2</v>
       </c>
       <c r="N25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O25" t="n">
         <v>3</v>
@@ -2020,7 +2092,7 @@
         <v>3</v>
       </c>
       <c r="Q25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R25" t="n">
         <v>1</v>
@@ -2031,6 +2103,9 @@
       <c r="T25" t="n">
         <v>1</v>
       </c>
+      <c r="U25" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -2039,60 +2114,63 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>9828</v>
+      </c>
+      <c r="C26" t="n">
         <v>10275</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>10626</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>11200</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>11475</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>11821</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>12115</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>12651</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>12991</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>12629</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>12453</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>11565</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>10968</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>10623</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>10465</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>9745</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>9280</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>8301</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>7828</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>7354</v>
       </c>
     </row>
@@ -2103,60 +2181,63 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>-25</v>
+      </c>
+      <c r="C27" t="n">
         <v>137</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>339</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>170</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>186</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>103</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>56</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>-109</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>-88</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>-51</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>-50</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>-123</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>-90</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>-64</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>9</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>8</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>14</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>12</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>-10</v>
       </c>
     </row>
@@ -2167,60 +2248,63 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>219157</v>
+      </c>
+      <c r="C28" t="n">
         <v>185038</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>107908</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>88737</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>72158</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>53950</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>45961</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>36598</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>20360</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>14921</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>12115</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>9905</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>12971</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>15758</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>25359</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>22995</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>20721</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>17550</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>16313</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>15790</v>
       </c>
     </row>
@@ -2231,60 +2315,63 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>228984</v>
+      </c>
+      <c r="C29" t="n">
         <v>195474</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>118897</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>100131</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>83843</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>65899</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>58157</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>49142</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>33265</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>27501</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>24520</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>21349</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>23851</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>26320</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>23798</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>21147</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>18774</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>15334</v>
       </c>
-      <c r="S29" t="n">
+      <c r="T29" t="n">
         <v>13914</v>
       </c>
-      <c r="T29" t="n">
+      <c r="U29" t="n">
         <v>13099</v>
       </c>
     </row>
@@ -2295,60 +2382,63 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>76926</v>
+      </c>
+      <c r="C30" t="n">
         <v>67335</v>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>49122</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>45152</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>38457</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>29380</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>26237</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>23851</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>12762</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>10240</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>10241</v>
       </c>
-      <c r="L30" t="n">
+      <c r="M30" t="n">
         <v>10343</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>14024</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>16451</v>
       </c>
-      <c r="O30" t="n">
+      <c r="P30" t="n">
         <v>18010</v>
       </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
         <v>14026</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="R30" t="n">
         <v>11689</v>
       </c>
-      <c r="R30" t="n">
+      <c r="S30" t="n">
         <v>7888</v>
       </c>
-      <c r="S30" t="n">
+      <c r="T30" t="n">
         <v>7707</v>
       </c>
-      <c r="T30" t="n">
+      <c r="U30" t="n">
         <v>860</v>
       </c>
     </row>
@@ -2398,21 +2488,24 @@
         <v>0</v>
       </c>
       <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
         <v>-12038</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>-11604</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>-11242</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>-10530</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>-10232</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>-10036</v>
       </c>
     </row>
@@ -2427,65 +2520,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T20"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46138</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45956</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45865</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45774</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45592</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45501</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45410</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45228</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45137</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45046</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44864</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44773</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44682</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44500</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44409</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44318</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44129</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44038</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43947</v>
       </c>
     </row>
@@ -2496,60 +2592,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>96221</v>
+      </c>
+      <c r="C2" t="n">
         <v>81615</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>57006</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>46743</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>44062</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>35082</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>30040</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>26044</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>18120</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>13507</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>7192</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>5931</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>6704</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>8288</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>7103</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>6507</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>5661</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>4726</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>3866</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>3080</v>
       </c>
     </row>
@@ -2560,60 +2659,63 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>24079</v>
+      </c>
+      <c r="C3" t="n">
         <v>20458</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>15157</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>12890</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>17394</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>8926</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>7466</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>5638</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>4720</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>4045</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>2544</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>2754</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>3789</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>2857</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>2472</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>2292</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>2032</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>1766</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>1591</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>1076</v>
       </c>
     </row>
@@ -2624,60 +2726,63 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>72142</v>
+      </c>
+      <c r="C4" t="n">
         <v>61157</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>41849</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>33853</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>26668</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>26156</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>22574</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>20406</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>13400</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>9462</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>4648</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>3177</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>2915</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>5431</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>4631</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>4215</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>3629</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>2960</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>2275</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>2004</v>
       </c>
     </row>
@@ -2688,60 +2793,63 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>7054</v>
+      </c>
+      <c r="C5" t="n">
         <v>6321</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>4705</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>4291</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>3989</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>3390</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>3090</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>2720</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>2294</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>2040</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>1875</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>1945</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>1824</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>1618</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>1403</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>1245</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>1153</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>1047</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>997</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>735</v>
       </c>
     </row>
@@ -2752,60 +2860,63 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>1354</v>
+      </c>
+      <c r="C6" t="n">
         <v>1300</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>1134</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>1122</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>1041</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>897</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>842</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>777</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>689</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>622</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>633</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>631</v>
-      </c>
-      <c r="M6" t="n">
-        <v>592</v>
       </c>
       <c r="N6" t="n">
         <v>592</v>
       </c>
       <c r="O6" t="n">
+        <v>592</v>
+      </c>
+      <c r="P6" t="n">
         <v>557</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>526</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>520</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>515</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>627</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>293</v>
       </c>
     </row>
@@ -2816,60 +2927,63 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>8408</v>
+      </c>
+      <c r="C7" t="n">
         <v>7621</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>5839</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>5413</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>5030</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>4287</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>3932</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>3497</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>2983</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>2662</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>2508</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>2576</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>2416</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>3563</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>1960</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>1771</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>1673</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>1562</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>1624</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>1028</v>
       </c>
     </row>
@@ -2880,765 +2994,801 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>63734</v>
+      </c>
+      <c r="C8" t="n">
         <v>53536</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>36010</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>28440</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>21638</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>21869</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>18642</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>16909</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>10417</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>6800</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>2140</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>601</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>499</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>1868</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>2671</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>2444</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>1956</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>1398</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>651</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>976</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Investment Income, Interest</t>
+          <t>Nonoperating Income (Expense)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>540</v>
+        <v>7773</v>
       </c>
       <c r="C9" t="n">
-        <v>624</v>
+        <v>16367</v>
       </c>
       <c r="D9" t="n">
-        <v>592</v>
+        <v>1926</v>
       </c>
       <c r="E9" t="n">
-        <v>515</v>
+        <v>2766</v>
       </c>
       <c r="F9" t="n">
-        <v>472</v>
+        <v>272</v>
       </c>
       <c r="G9" t="n">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="H9" t="n">
-        <v>359</v>
+        <v>572</v>
       </c>
       <c r="I9" t="n">
-        <v>234</v>
+        <v>370</v>
       </c>
       <c r="J9" t="n">
-        <v>187</v>
+        <v>105</v>
       </c>
       <c r="K9" t="n">
-        <v>150</v>
+        <v>181</v>
       </c>
       <c r="L9" t="n">
+        <v>69</v>
+      </c>
+      <c r="M9" t="n">
+        <v>12</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-24</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-63</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-33</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>-50</v>
+      </c>
+      <c r="R9" t="n">
         <v>88</v>
       </c>
-      <c r="M9" t="n">
-        <v>46</v>
-      </c>
-      <c r="N9" t="n">
-        <v>18</v>
-      </c>
-      <c r="O9" t="n">
-        <v>7</v>
-      </c>
-      <c r="P9" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>6</v>
-      </c>
-      <c r="R9" t="n">
-        <v>7</v>
-      </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>-50</v>
       </c>
       <c r="T9" t="n">
-        <v>31</v>
+        <v>-42</v>
+      </c>
+      <c r="U9" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Interest Expense</t>
+          <t>Income Before Provision for Income Taxes</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>102</v>
+        <v>71507</v>
       </c>
       <c r="C10" t="n">
-        <v>61</v>
+        <v>69903</v>
       </c>
       <c r="D10" t="n">
-        <v>62</v>
+        <v>37936</v>
       </c>
       <c r="E10" t="n">
-        <v>63</v>
+        <v>31206</v>
       </c>
       <c r="F10" t="n">
-        <v>61</v>
+        <v>21910</v>
       </c>
       <c r="G10" t="n">
-        <v>61</v>
+        <v>22316</v>
       </c>
       <c r="H10" t="n">
-        <v>64</v>
+        <v>19214</v>
       </c>
       <c r="I10" t="n">
-        <v>63</v>
+        <v>17279</v>
       </c>
       <c r="J10" t="n">
-        <v>65</v>
+        <v>10522</v>
       </c>
       <c r="K10" t="n">
-        <v>66</v>
+        <v>6981</v>
       </c>
       <c r="L10" t="n">
-        <v>65</v>
+        <v>2209</v>
       </c>
       <c r="M10" t="n">
-        <v>65</v>
+        <v>613</v>
       </c>
       <c r="N10" t="n">
-        <v>68</v>
+        <v>475</v>
       </c>
       <c r="O10" t="n">
-        <v>62</v>
+        <v>1805</v>
       </c>
       <c r="P10" t="n">
-        <v>60</v>
+        <v>2638</v>
       </c>
       <c r="Q10" t="n">
-        <v>53</v>
+        <v>2394</v>
       </c>
       <c r="R10" t="n">
-        <v>53</v>
+        <v>2044</v>
       </c>
       <c r="S10" t="n">
-        <v>54</v>
+        <v>1348</v>
       </c>
       <c r="T10" t="n">
-        <v>25</v>
+        <v>609</v>
+      </c>
+      <c r="U10" t="n">
+        <v>981</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Other Nonoperating Income (Expense)</t>
+          <t>Provision for Income Taxes</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15929</v>
+        <v>11819</v>
       </c>
       <c r="C11" t="n">
-        <v>1363</v>
+        <v>11582</v>
       </c>
       <c r="D11" t="n">
-        <v>2236</v>
+        <v>6026</v>
       </c>
       <c r="E11" t="n">
-        <v>-180</v>
+        <v>4784</v>
       </c>
       <c r="F11" t="n">
-        <v>36</v>
+        <v>3135</v>
       </c>
       <c r="G11" t="n">
-        <v>189</v>
+        <v>3007</v>
       </c>
       <c r="H11" t="n">
-        <v>75</v>
+        <v>2615</v>
       </c>
       <c r="I11" t="n">
-        <v>-66</v>
+        <v>2398</v>
       </c>
       <c r="J11" t="n">
-        <v>59</v>
+        <v>1279</v>
       </c>
       <c r="K11" t="n">
-        <v>-15</v>
+        <v>793</v>
       </c>
       <c r="L11" t="n">
-        <v>-11</v>
+        <v>166</v>
       </c>
       <c r="M11" t="n">
-        <v>-5</v>
+        <v>-67</v>
       </c>
       <c r="N11" t="n">
+        <v>-181</v>
+      </c>
+      <c r="O11" t="n">
+        <v>187</v>
+      </c>
+      <c r="P11" t="n">
+        <v>174</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>20</v>
+      </c>
+      <c r="R11" t="n">
+        <v>132</v>
+      </c>
+      <c r="S11" t="n">
+        <v>12</v>
+      </c>
+      <c r="T11" t="n">
         <v>-13</v>
       </c>
-      <c r="O11" t="n">
-        <v>22</v>
-      </c>
-      <c r="P11" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>135</v>
-      </c>
-      <c r="R11" t="n">
-        <v>-4</v>
-      </c>
-      <c r="S11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="T11" t="n">
-        <v>-1</v>
+      <c r="U11" t="n">
+        <v>64</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Nonoperating Income (Expense)</t>
+          <t>Net Income</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16367</v>
+        <v>59688</v>
       </c>
       <c r="C12" t="n">
-        <v>1926</v>
+        <v>58321</v>
       </c>
       <c r="D12" t="n">
-        <v>2766</v>
+        <v>31910</v>
       </c>
       <c r="E12" t="n">
-        <v>272</v>
+        <v>26422</v>
       </c>
       <c r="F12" t="n">
-        <v>447</v>
+        <v>18775</v>
       </c>
       <c r="G12" t="n">
-        <v>572</v>
+        <v>19309</v>
       </c>
       <c r="H12" t="n">
-        <v>370</v>
+        <v>16599</v>
       </c>
       <c r="I12" t="n">
-        <v>105</v>
+        <v>14881</v>
       </c>
       <c r="J12" t="n">
-        <v>181</v>
+        <v>9243</v>
       </c>
       <c r="K12" t="n">
-        <v>69</v>
+        <v>6188</v>
       </c>
       <c r="L12" t="n">
-        <v>12</v>
+        <v>2043</v>
       </c>
       <c r="M12" t="n">
-        <v>-24</v>
+        <v>680</v>
       </c>
       <c r="N12" t="n">
-        <v>-63</v>
+        <v>656</v>
       </c>
       <c r="O12" t="n">
-        <v>-33</v>
+        <v>1618</v>
       </c>
       <c r="P12" t="n">
-        <v>-50</v>
+        <v>2464</v>
       </c>
       <c r="Q12" t="n">
-        <v>88</v>
+        <v>2374</v>
       </c>
       <c r="R12" t="n">
-        <v>-50</v>
+        <v>1912</v>
       </c>
       <c r="S12" t="n">
-        <v>-42</v>
+        <v>1336</v>
       </c>
       <c r="T12" t="n">
-        <v>5</v>
+        <v>622</v>
+      </c>
+      <c r="U12" t="n">
+        <v>917</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Income Before Provision for Income Taxes</t>
+          <t>Earnings Per Share, Basic</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>69903</v>
+        <v>2.47</v>
       </c>
       <c r="C13" t="n">
-        <v>37936</v>
+        <v>2.4</v>
       </c>
       <c r="D13" t="n">
-        <v>31206</v>
+        <v>1.31</v>
       </c>
       <c r="E13" t="n">
-        <v>21910</v>
+        <v>1.08</v>
       </c>
       <c r="F13" t="n">
-        <v>22316</v>
+        <v>0.77</v>
       </c>
       <c r="G13" t="n">
-        <v>19214</v>
+        <v>0.79</v>
       </c>
       <c r="H13" t="n">
-        <v>17279</v>
+        <v>0.68</v>
       </c>
       <c r="I13" t="n">
-        <v>10522</v>
+        <v>6.04</v>
       </c>
       <c r="J13" t="n">
-        <v>6981</v>
+        <v>3.75</v>
       </c>
       <c r="K13" t="n">
-        <v>2209</v>
+        <v>2.5</v>
       </c>
       <c r="L13" t="n">
-        <v>613</v>
+        <v>0.83</v>
       </c>
       <c r="M13" t="n">
-        <v>475</v>
+        <v>0.27</v>
       </c>
       <c r="N13" t="n">
-        <v>1805</v>
+        <v>0.26</v>
       </c>
       <c r="O13" t="n">
-        <v>2638</v>
+        <v>0.65</v>
       </c>
       <c r="P13" t="n">
-        <v>2394</v>
+        <v>0.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>2044</v>
+        <v>0.95</v>
       </c>
       <c r="R13" t="n">
-        <v>1348</v>
+        <v>3.08</v>
       </c>
       <c r="S13" t="n">
-        <v>609</v>
+        <v>2.16</v>
       </c>
       <c r="T13" t="n">
-        <v>981</v>
+        <v>1.01</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Provision for Income Taxes</t>
+          <t>Earnings Per Share, Diluted</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>11582</v>
+        <v>2.46</v>
       </c>
       <c r="C14" t="n">
-        <v>6026</v>
+        <v>2.39</v>
       </c>
       <c r="D14" t="n">
-        <v>4784</v>
+        <v>1.3</v>
       </c>
       <c r="E14" t="n">
-        <v>3135</v>
+        <v>1.08</v>
       </c>
       <c r="F14" t="n">
-        <v>3007</v>
+        <v>0.76</v>
       </c>
       <c r="G14" t="n">
-        <v>2615</v>
+        <v>0.78</v>
       </c>
       <c r="H14" t="n">
-        <v>2398</v>
+        <v>0.67</v>
       </c>
       <c r="I14" t="n">
-        <v>1279</v>
+        <v>5.98</v>
       </c>
       <c r="J14" t="n">
-        <v>793</v>
+        <v>3.71</v>
       </c>
       <c r="K14" t="n">
-        <v>166</v>
+        <v>2.48</v>
       </c>
       <c r="L14" t="n">
-        <v>-67</v>
+        <v>0.82</v>
       </c>
       <c r="M14" t="n">
-        <v>-181</v>
+        <v>0.27</v>
       </c>
       <c r="N14" t="n">
-        <v>187</v>
+        <v>0.26</v>
       </c>
       <c r="O14" t="n">
-        <v>174</v>
+        <v>0.64</v>
       </c>
       <c r="P14" t="n">
-        <v>20</v>
+        <v>0.97</v>
       </c>
       <c r="Q14" t="n">
-        <v>132</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>12</v>
+        <v>3.03</v>
       </c>
       <c r="S14" t="n">
-        <v>-13</v>
+        <v>2.12</v>
       </c>
       <c r="T14" t="n">
-        <v>64</v>
+        <v>0.99</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Net Income</t>
+          <t>Number of Shares - Basic</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58321</v>
+        <v>24190</v>
       </c>
       <c r="C15" t="n">
-        <v>31910</v>
+        <v>24286</v>
       </c>
       <c r="D15" t="n">
-        <v>26422</v>
+        <v>24327</v>
       </c>
       <c r="E15" t="n">
-        <v>18775</v>
+        <v>24366</v>
       </c>
       <c r="F15" t="n">
-        <v>19309</v>
+        <v>24441</v>
       </c>
       <c r="G15" t="n">
-        <v>16599</v>
+        <v>24533</v>
       </c>
       <c r="H15" t="n">
-        <v>14881</v>
+        <v>24578</v>
       </c>
       <c r="I15" t="n">
-        <v>9243</v>
+        <v>2462</v>
       </c>
       <c r="J15" t="n">
-        <v>6188</v>
+        <v>2468</v>
       </c>
       <c r="K15" t="n">
-        <v>2043</v>
+        <v>2473</v>
       </c>
       <c r="L15" t="n">
-        <v>680</v>
+        <v>2470</v>
       </c>
       <c r="M15" t="n">
-        <v>656</v>
+        <v>2483</v>
       </c>
       <c r="N15" t="n">
-        <v>1618</v>
+        <v>2495</v>
       </c>
       <c r="O15" t="n">
-        <v>2464</v>
+        <v>2506</v>
       </c>
       <c r="P15" t="n">
-        <v>2374</v>
+        <v>2499</v>
       </c>
       <c r="Q15" t="n">
-        <v>1912</v>
+        <v>2493</v>
       </c>
       <c r="R15" t="n">
-        <v>1336</v>
+        <v>621</v>
       </c>
       <c r="S15" t="n">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="T15" t="n">
-        <v>917</v>
+        <v>616</v>
+      </c>
+      <c r="U15" t="n">
+        <v>614</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Earnings Per Share, Basic</t>
+          <t>Number of Shares - Diluted</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.4</v>
+        <v>24285</v>
       </c>
       <c r="C16" t="n">
-        <v>1.31</v>
+        <v>24391</v>
       </c>
       <c r="D16" t="n">
-        <v>1.08</v>
+        <v>24483</v>
       </c>
       <c r="E16" t="n">
-        <v>0.77</v>
+        <v>24532</v>
       </c>
       <c r="F16" t="n">
-        <v>0.79</v>
+        <v>24611</v>
       </c>
       <c r="G16" t="n">
-        <v>0.68</v>
+        <v>24774</v>
       </c>
       <c r="H16" t="n">
-        <v>6.04</v>
+        <v>24848</v>
       </c>
       <c r="I16" t="n">
-        <v>3.75</v>
+        <v>2489</v>
       </c>
       <c r="J16" t="n">
-        <v>2.5</v>
+        <v>2494</v>
       </c>
       <c r="K16" t="n">
-        <v>0.83</v>
+        <v>2499</v>
       </c>
       <c r="L16" t="n">
-        <v>0.27</v>
+        <v>2490</v>
       </c>
       <c r="M16" t="n">
-        <v>0.26</v>
+        <v>2499</v>
       </c>
       <c r="N16" t="n">
-        <v>0.65</v>
+        <v>2516</v>
       </c>
       <c r="O16" t="n">
-        <v>0.99</v>
+        <v>2537</v>
       </c>
       <c r="P16" t="n">
-        <v>0.95</v>
+        <v>2538</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.08</v>
+        <v>2532</v>
       </c>
       <c r="R16" t="n">
-        <v>2.16</v>
+        <v>632</v>
       </c>
       <c r="S16" t="n">
-        <v>1.01</v>
+        <v>630</v>
       </c>
       <c r="T16" t="n">
-        <v>1.49</v>
+        <v>626</v>
+      </c>
+      <c r="U16" t="n">
+        <v>622</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Earnings Per Share, Diluted</t>
+          <t>Investment Income, Interest</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>1.3</v>
+        <v>540</v>
       </c>
       <c r="D17" t="n">
-        <v>1.08</v>
+        <v>624</v>
       </c>
       <c r="E17" t="n">
-        <v>0.76</v>
+        <v>592</v>
       </c>
       <c r="F17" t="n">
-        <v>0.78</v>
+        <v>515</v>
       </c>
       <c r="G17" t="n">
-        <v>0.67</v>
+        <v>472</v>
       </c>
       <c r="H17" t="n">
-        <v>5.98</v>
+        <v>444</v>
       </c>
       <c r="I17" t="n">
-        <v>3.71</v>
+        <v>359</v>
       </c>
       <c r="J17" t="n">
-        <v>2.48</v>
+        <v>234</v>
       </c>
       <c r="K17" t="n">
-        <v>0.82</v>
+        <v>187</v>
       </c>
       <c r="L17" t="n">
-        <v>0.27</v>
+        <v>150</v>
       </c>
       <c r="M17" t="n">
-        <v>0.26</v>
+        <v>88</v>
       </c>
       <c r="N17" t="n">
-        <v>0.64</v>
+        <v>46</v>
       </c>
       <c r="O17" t="n">
-        <v>0.97</v>
+        <v>18</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9399999999999999</v>
+        <v>7</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.03</v>
+        <v>6</v>
       </c>
       <c r="R17" t="n">
-        <v>2.12</v>
+        <v>6</v>
       </c>
       <c r="S17" t="n">
-        <v>0.99</v>
+        <v>7</v>
       </c>
       <c r="T17" t="n">
-        <v>1.47</v>
+        <v>13</v>
+      </c>
+      <c r="U17" t="n">
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Number of Shares - Basic</t>
+          <t>Interest Expense</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24286</v>
+        <v>227</v>
       </c>
       <c r="C18" t="n">
-        <v>24327</v>
+        <v>102</v>
       </c>
       <c r="D18" t="n">
-        <v>24366</v>
+        <v>61</v>
       </c>
       <c r="E18" t="n">
-        <v>24441</v>
+        <v>62</v>
       </c>
       <c r="F18" t="n">
-        <v>24533</v>
+        <v>63</v>
       </c>
       <c r="G18" t="n">
-        <v>24578</v>
+        <v>61</v>
       </c>
       <c r="H18" t="n">
-        <v>2462</v>
+        <v>61</v>
       </c>
       <c r="I18" t="n">
-        <v>2468</v>
+        <v>64</v>
       </c>
       <c r="J18" t="n">
-        <v>2473</v>
+        <v>63</v>
       </c>
       <c r="K18" t="n">
-        <v>2470</v>
+        <v>65</v>
       </c>
       <c r="L18" t="n">
-        <v>2483</v>
+        <v>66</v>
       </c>
       <c r="M18" t="n">
-        <v>2495</v>
+        <v>65</v>
       </c>
       <c r="N18" t="n">
-        <v>2506</v>
+        <v>65</v>
       </c>
       <c r="O18" t="n">
-        <v>2499</v>
+        <v>68</v>
       </c>
       <c r="P18" t="n">
-        <v>2493</v>
+        <v>62</v>
       </c>
       <c r="Q18" t="n">
-        <v>621</v>
+        <v>60</v>
       </c>
       <c r="R18" t="n">
-        <v>618</v>
+        <v>53</v>
       </c>
       <c r="S18" t="n">
-        <v>616</v>
+        <v>53</v>
       </c>
       <c r="T18" t="n">
-        <v>614</v>
+        <v>54</v>
+      </c>
+      <c r="U18" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Number of Shares - Diluted</t>
+          <t>Other Nonoperating Income (Expense)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24391</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>24483</v>
+        <v>15929</v>
       </c>
       <c r="D19" t="n">
-        <v>24532</v>
+        <v>1363</v>
       </c>
       <c r="E19" t="n">
-        <v>24611</v>
+        <v>2236</v>
       </c>
       <c r="F19" t="n">
-        <v>24774</v>
+        <v>-180</v>
       </c>
       <c r="G19" t="n">
-        <v>24848</v>
+        <v>36</v>
       </c>
       <c r="H19" t="n">
-        <v>2489</v>
+        <v>189</v>
       </c>
       <c r="I19" t="n">
-        <v>2494</v>
+        <v>75</v>
       </c>
       <c r="J19" t="n">
-        <v>2499</v>
+        <v>-66</v>
       </c>
       <c r="K19" t="n">
-        <v>2490</v>
+        <v>59</v>
       </c>
       <c r="L19" t="n">
-        <v>2499</v>
+        <v>-15</v>
       </c>
       <c r="M19" t="n">
-        <v>2516</v>
+        <v>-11</v>
       </c>
       <c r="N19" t="n">
-        <v>2537</v>
+        <v>-5</v>
       </c>
       <c r="O19" t="n">
-        <v>2538</v>
+        <v>-13</v>
       </c>
       <c r="P19" t="n">
-        <v>2532</v>
+        <v>22</v>
       </c>
       <c r="Q19" t="n">
-        <v>632</v>
+        <v>4</v>
       </c>
       <c r="R19" t="n">
-        <v>630</v>
+        <v>135</v>
       </c>
       <c r="S19" t="n">
-        <v>626</v>
+        <v>-4</v>
       </c>
       <c r="T19" t="n">
-        <v>622</v>
+        <v>-1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="20">
@@ -3684,11 +3834,11 @@
         <v>0</v>
       </c>
       <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>1353</v>
       </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
       <c r="P20" t="n">
         <v>0</v>
       </c>
@@ -3702,6 +3852,9 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3716,65 +3869,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T37"/>
+  <dimension ref="A1:U41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46138</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45956</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45865</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45774</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45592</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45501</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45410</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45228</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45137</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45046</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44864</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44773</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44682</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44500</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44409</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44318</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44129</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44038</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43947</v>
       </c>
     </row>
@@ -3785,60 +3941,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>118010</v>
+      </c>
+      <c r="C2" t="n">
         <v>58321</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>77107</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>45197</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>18775</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>50789</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>31480</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>14881</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>17475</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>8232</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>2043</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>2954</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>2274</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>1618</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>6749</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>4285</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>1912</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>2875</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>1539</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>917</v>
       </c>
     </row>
@@ -3849,189 +4008,198 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>3954</v>
+      </c>
+      <c r="C3" t="n">
         <v>1928</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>4753</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>3099</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>1474</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>3416</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>2164</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>1011</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>2555</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>1576</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>735</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>1971</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>1226</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>578</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>1453</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>894</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>429</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>981</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>598</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>224</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Deferred Income Tax Expense (Benefit)</t>
+          <t>Depreciation, Depletion and Amortization</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1584</v>
+        <v>2124</v>
       </c>
       <c r="C4" t="n">
-        <v>-2035</v>
+        <v>997</v>
       </c>
       <c r="D4" t="n">
-        <v>-2160</v>
+        <v>2031</v>
       </c>
       <c r="E4" t="n">
-        <v>-2177</v>
+        <v>1280</v>
       </c>
       <c r="F4" t="n">
-        <v>-3879</v>
+        <v>611</v>
       </c>
       <c r="G4" t="n">
-        <v>-3276</v>
+        <v>1321</v>
       </c>
       <c r="H4" t="n">
-        <v>-1577</v>
+        <v>843</v>
       </c>
       <c r="I4" t="n">
-        <v>-2411</v>
+        <v>410</v>
       </c>
       <c r="J4" t="n">
-        <v>-1881</v>
+        <v>1121</v>
       </c>
       <c r="K4" t="n">
-        <v>-1135</v>
+        <v>749</v>
       </c>
       <c r="L4" t="n">
-        <v>-1517</v>
+        <v>384</v>
       </c>
       <c r="M4" t="n">
-        <v>-985</v>
+        <v>1118</v>
       </c>
       <c r="N4" t="n">
-        <v>-542</v>
+        <v>712</v>
       </c>
       <c r="O4" t="n">
-        <v>-182</v>
+        <v>334</v>
       </c>
       <c r="P4" t="n">
-        <v>-161</v>
+        <v>865</v>
       </c>
       <c r="Q4" t="n">
-        <v>24</v>
+        <v>567</v>
       </c>
       <c r="R4" t="n">
-        <v>-117</v>
+        <v>281</v>
       </c>
       <c r="S4" t="n">
-        <v>-64</v>
+        <v>810</v>
       </c>
       <c r="T4" t="n">
-        <v>16</v>
+        <v>511</v>
+      </c>
+      <c r="U4" t="n">
+        <v>107</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Depreciation, Depletion and Amortization</t>
+          <t>Deferred Income Tax Expense (Benefit)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>997</v>
+        <v>982</v>
       </c>
       <c r="C5" t="n">
-        <v>2031</v>
+        <v>1584</v>
       </c>
       <c r="D5" t="n">
-        <v>1280</v>
+        <v>-2035</v>
       </c>
       <c r="E5" t="n">
-        <v>611</v>
+        <v>-2160</v>
       </c>
       <c r="F5" t="n">
-        <v>1321</v>
+        <v>-2177</v>
       </c>
       <c r="G5" t="n">
-        <v>843</v>
+        <v>-3879</v>
       </c>
       <c r="H5" t="n">
-        <v>410</v>
+        <v>-3276</v>
       </c>
       <c r="I5" t="n">
-        <v>1121</v>
+        <v>-1577</v>
       </c>
       <c r="J5" t="n">
-        <v>749</v>
+        <v>-2411</v>
       </c>
       <c r="K5" t="n">
-        <v>384</v>
+        <v>-1881</v>
       </c>
       <c r="L5" t="n">
-        <v>1118</v>
+        <v>-1135</v>
       </c>
       <c r="M5" t="n">
-        <v>712</v>
+        <v>-1517</v>
       </c>
       <c r="N5" t="n">
-        <v>334</v>
+        <v>-985</v>
       </c>
       <c r="O5" t="n">
-        <v>865</v>
+        <v>-542</v>
       </c>
       <c r="P5" t="n">
-        <v>567</v>
+        <v>-182</v>
       </c>
       <c r="Q5" t="n">
-        <v>281</v>
+        <v>-161</v>
       </c>
       <c r="R5" t="n">
-        <v>810</v>
+        <v>24</v>
       </c>
       <c r="S5" t="n">
-        <v>511</v>
+        <v>-117</v>
       </c>
       <c r="T5" t="n">
-        <v>107</v>
+        <v>-64</v>
+      </c>
+      <c r="U5" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -4041,60 +4209,63 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>-23707</v>
+      </c>
+      <c r="C6" t="n">
         <v>-15936</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>-3426</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>-2073</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>175</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>-302</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>-264</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>-69</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>24</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>-45</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>14</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>35</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>24</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>17</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>-152</v>
-      </c>
-      <c r="P6" t="n">
-        <v>-133</v>
       </c>
       <c r="Q6" t="n">
         <v>-133</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-133</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4105,60 +4276,63 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>222</v>
+      </c>
+      <c r="C7" t="n">
         <v>-94</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>-276</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>-196</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>-98</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>-365</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>-288</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>-145</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>-170</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>-102</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>-34</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>-27</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>18</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>23</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>25</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>16</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>-3</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>-2</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>-5</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>4</v>
       </c>
     </row>
@@ -4169,60 +4343,63 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>-24590</v>
+      </c>
+      <c r="C8" t="n">
         <v>-2243</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>-10325</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>-4743</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>933</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>-7694</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>-4133</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>-2366</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>-4482</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>-3239</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>-252</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>-258</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>-668</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>-788</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>-1523</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>-1157</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>-595</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>-667</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>-205</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>-249</v>
       </c>
     </row>
@@ -4233,60 +4410,63 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>-10204</v>
+      </c>
+      <c r="C9" t="n">
         <v>-4420</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>-9703</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>-4880</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>-1258</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>-2357</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>-1380</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>-577</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>405</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>861</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>566</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>-1848</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>-1285</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>-560</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>-400</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>-282</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>-159</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>-190</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>-97</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>-151</v>
       </c>
     </row>
@@ -4297,60 +4477,63 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>-6480</v>
+      </c>
+      <c r="C10" t="n">
         <v>-983</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>857</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>946</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>560</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>-726</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>-12</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>-726</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>-337</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>-592</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>-215</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>-1307</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>-1554</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>-1261</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>-1557</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>18</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>2</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>-409</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>34</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>-8</v>
       </c>
     </row>
@@ -4361,60 +4544,63 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>4125</v>
+      </c>
+      <c r="C11" t="n">
         <v>2210</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>2032</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>2255</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>941</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>2490</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>801</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>-22</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>1250</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>789</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>11</v>
       </c>
-      <c r="L11" t="n">
+      <c r="M11" t="n">
         <v>-358</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>559</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>255</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>474</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>279</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>70</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>289</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>63</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>71</v>
       </c>
     </row>
@@ -4425,60 +4611,63 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>8015</v>
+      </c>
+      <c r="C12" t="n">
         <v>7763</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>4204</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>3075</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>7128</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>3918</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>3314</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>4202</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>953</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>2675</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>689</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>1175</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>1267</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>634</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>70</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>132</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>-1</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>111</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>81</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>-32</v>
       </c>
     </row>
@@ -4489,60 +4678,63 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>1970</v>
+      </c>
+      <c r="C13" t="n">
         <v>1217</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>1311</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>979</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>350</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>849</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>584</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>323</v>
       </c>
-      <c r="I13" t="n">
+      <c r="J13" t="n">
         <v>208</v>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>236</v>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>105</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>102</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>60</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>70</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>253</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>98</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>47</v>
       </c>
-      <c r="R13" t="n">
+      <c r="S13" t="n">
         <v>74</v>
       </c>
-      <c r="S13" t="n">
+      <c r="T13" t="n">
         <v>21</v>
       </c>
-      <c r="T13" t="n">
+      <c r="U13" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4553,153 +4745,159 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>74421</v>
+      </c>
+      <c r="C14" t="n">
         <v>50344</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>66530</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>42779</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>27414</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>47460</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>29833</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>15345</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>16591</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>9259</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>2911</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>3393</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>3001</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>1731</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>6075</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>4556</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>1874</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>3755</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>2476</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>909</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Maturities, Prepayments and Calls of Debt Securities, Available-for-sale</t>
+          <t>Proceeds from Sale and Maturity of Debt Securities, Available-for-sale</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1946</v>
+        <v>26563</v>
       </c>
       <c r="C15" t="n">
-        <v>8980</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>6252</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>3122</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>9485</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>8098</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>4004</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>8001</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>5111</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>2512</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>16792</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>10983</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>5947</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>7780</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>5236</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3140</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>5165</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1032</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Sale of Debt Securities, Available-for-sale</t>
+          <t>Proceeds From Sale Of Equity Securities</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25</v>
+        <v>7241</v>
       </c>
       <c r="C16" t="n">
-        <v>487</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>487</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>467</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -4711,1214 +4909,1271 @@
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1806</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1731</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1029</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>916</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>705</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>358</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>502</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>259</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Purchases Of Property And Equipment And Intangible Assets</t>
+          <t>Payments To Acquire Equity Securities</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-1757</v>
+        <v>-42404</v>
       </c>
       <c r="C17" t="n">
-        <v>-4758</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>-3122</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>-1227</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-2159</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>-1346</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>-369</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-815</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>-537</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>-248</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-1324</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-794</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-361</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-703</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>-481</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-298</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-845</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Payments to Acquire Businesses, Net of Cash Acquired</t>
+          <t>Payments to Acquire Debt Securities, Available-for-sale</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-87</v>
+        <v>-21777</v>
       </c>
       <c r="C18" t="n">
-        <v>-1370</v>
+        <v>-8000</v>
       </c>
       <c r="D18" t="n">
-        <v>-677</v>
+        <v>-20076</v>
       </c>
       <c r="E18" t="n">
-        <v>-383</v>
+        <v>-14358</v>
       </c>
       <c r="F18" t="n">
-        <v>-465</v>
+        <v>-6546</v>
       </c>
       <c r="G18" t="n">
-        <v>-317</v>
+        <v>-19565</v>
       </c>
       <c r="H18" t="n">
-        <v>-39</v>
+        <v>-15047</v>
       </c>
       <c r="I18" t="n">
-        <v>-83</v>
+        <v>-9303</v>
       </c>
       <c r="J18" t="n">
-        <v>-83</v>
+        <v>-10688</v>
       </c>
       <c r="K18" t="n">
-        <v>-83</v>
+        <v>-5343</v>
       </c>
       <c r="L18" t="n">
-        <v>-49</v>
+        <v>-2801</v>
       </c>
       <c r="M18" t="n">
-        <v>-49</v>
+        <v>-9764</v>
       </c>
       <c r="N18" t="n">
-        <v>-36</v>
+        <v>-7576</v>
       </c>
       <c r="O18" t="n">
-        <v>-203</v>
+        <v>-3932</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-16020</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-9268</v>
       </c>
       <c r="R18" t="n">
-        <v>-8524</v>
+        <v>-4470</v>
       </c>
       <c r="S18" t="n">
-        <v>-7171</v>
+        <v>-12840</v>
       </c>
       <c r="T18" t="n">
-        <v>-34</v>
+        <v>-8286</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-861</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Net Cash Provided by (Used in) Investing Activities</t>
+          <t>Purchases Of Property And Equipment And Intangible Assets</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-26429</v>
+        <v>-4434</v>
       </c>
       <c r="C19" t="n">
-        <v>-21367</v>
+        <v>-1757</v>
       </c>
       <c r="D19" t="n">
-        <v>-12343</v>
+        <v>-4758</v>
       </c>
       <c r="E19" t="n">
-        <v>-5216</v>
+        <v>-3122</v>
       </c>
       <c r="F19" t="n">
-        <v>-13223</v>
+        <v>-1227</v>
       </c>
       <c r="G19" t="n">
-        <v>-8877</v>
+        <v>-2159</v>
       </c>
       <c r="H19" t="n">
-        <v>-5693</v>
+        <v>-1346</v>
       </c>
       <c r="I19" t="n">
-        <v>-4457</v>
+        <v>-369</v>
       </c>
       <c r="J19" t="n">
-        <v>-1287</v>
+        <v>-815</v>
       </c>
       <c r="K19" t="n">
-        <v>-841</v>
+        <v>-537</v>
       </c>
       <c r="L19" t="n">
-        <v>7378</v>
+        <v>-248</v>
       </c>
       <c r="M19" t="n">
-        <v>4230</v>
+        <v>-1324</v>
       </c>
       <c r="N19" t="n">
-        <v>2612</v>
+        <v>-794</v>
       </c>
       <c r="O19" t="n">
-        <v>-8244</v>
+        <v>-361</v>
       </c>
       <c r="P19" t="n">
-        <v>-3805</v>
+        <v>-703</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1272</v>
+        <v>-481</v>
       </c>
       <c r="R19" t="n">
-        <v>-16546</v>
+        <v>-298</v>
       </c>
       <c r="S19" t="n">
-        <v>-14545</v>
+        <v>-845</v>
       </c>
       <c r="T19" t="n">
-        <v>-1055</v>
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Stock Plans</t>
+          <t>Payments to Acquire Businesses, Net of Cash Acquired</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>515</v>
+        <v>-298</v>
       </c>
       <c r="C20" t="n">
-        <v>643</v>
+        <v>-87</v>
       </c>
       <c r="D20" t="n">
-        <v>370</v>
+        <v>-1370</v>
       </c>
       <c r="E20" t="n">
-        <v>370</v>
+        <v>-677</v>
       </c>
       <c r="F20" t="n">
-        <v>489</v>
+        <v>-383</v>
       </c>
       <c r="G20" t="n">
-        <v>285</v>
+        <v>-465</v>
       </c>
       <c r="H20" t="n">
-        <v>285</v>
+        <v>-317</v>
       </c>
       <c r="I20" t="n">
-        <v>403</v>
+        <v>-39</v>
       </c>
       <c r="J20" t="n">
-        <v>247</v>
+        <v>-83</v>
       </c>
       <c r="K20" t="n">
-        <v>246</v>
+        <v>-83</v>
       </c>
       <c r="L20" t="n">
-        <v>349</v>
+        <v>-83</v>
       </c>
       <c r="M20" t="n">
-        <v>205</v>
+        <v>-49</v>
       </c>
       <c r="N20" t="n">
-        <v>204</v>
+        <v>-49</v>
       </c>
       <c r="O20" t="n">
-        <v>277</v>
+        <v>-36</v>
       </c>
       <c r="P20" t="n">
-        <v>128</v>
+        <v>-203</v>
       </c>
       <c r="Q20" t="n">
-        <v>126</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>94</v>
+        <v>-8524</v>
       </c>
       <c r="T20" t="n">
-        <v>88</v>
+        <v>-7171</v>
+      </c>
+      <c r="U20" t="n">
+        <v>-34</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Payments for Repurchase of Common Stock</t>
+          <t>Payments for (Proceeds from) Other Investing Activities</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-19312</v>
+        <v>-15</v>
       </c>
       <c r="C21" t="n">
-        <v>-36271</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>-23815</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>-14095</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-25895</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-14898</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-7740</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>-6874</v>
+        <v>-135</v>
       </c>
       <c r="J21" t="n">
-        <v>-3067</v>
+        <v>-872</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-435</v>
       </c>
       <c r="L21" t="n">
-        <v>-8826</v>
+        <v>-221</v>
       </c>
       <c r="M21" t="n">
-        <v>-5341</v>
+        <v>-83</v>
       </c>
       <c r="N21" t="n">
-        <v>-1996</v>
+        <v>-65</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>-35</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-7</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Payment, Tax Withholding, Share-based Payment Arrangement</t>
+          <t>Net Cash Provided by (Used in) Investing Activities</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-2129</v>
+        <v>-35124</v>
       </c>
       <c r="C22" t="n">
-        <v>-5809</v>
+        <v>-26429</v>
       </c>
       <c r="D22" t="n">
-        <v>-3380</v>
+        <v>-21367</v>
       </c>
       <c r="E22" t="n">
-        <v>-1532</v>
+        <v>-12343</v>
       </c>
       <c r="F22" t="n">
-        <v>-5068</v>
+        <v>-5216</v>
       </c>
       <c r="G22" t="n">
-        <v>-3389</v>
+        <v>-13223</v>
       </c>
       <c r="H22" t="n">
-        <v>-1752</v>
+        <v>-8877</v>
       </c>
       <c r="I22" t="n">
-        <v>-1942</v>
+        <v>-5693</v>
       </c>
       <c r="J22" t="n">
-        <v>-1179</v>
+        <v>-4457</v>
       </c>
       <c r="K22" t="n">
-        <v>-507</v>
+        <v>-1287</v>
       </c>
       <c r="L22" t="n">
-        <v>-1131</v>
+        <v>-841</v>
       </c>
       <c r="M22" t="n">
-        <v>-837</v>
+        <v>7378</v>
       </c>
       <c r="N22" t="n">
-        <v>-532</v>
+        <v>4230</v>
       </c>
       <c r="O22" t="n">
-        <v>-1282</v>
+        <v>2612</v>
       </c>
       <c r="P22" t="n">
-        <v>-843</v>
+        <v>-8244</v>
       </c>
       <c r="Q22" t="n">
-        <v>-477</v>
+        <v>-3805</v>
       </c>
       <c r="R22" t="n">
-        <v>-716</v>
+        <v>-1272</v>
       </c>
       <c r="S22" t="n">
-        <v>-418</v>
+        <v>-16546</v>
       </c>
       <c r="T22" t="n">
-        <v>-222</v>
+        <v>-14545</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-1055</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Payments of Dividends</t>
+          <t>Proceeds from Debt, Net of Issuance Costs</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>-243</v>
+        <v>24896</v>
       </c>
       <c r="C23" t="n">
-        <v>-732</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>-488</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>-244</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>-589</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>-344</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>-98</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>-296</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>-199</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>-99</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>-298</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>-198</v>
+        <v>4977</v>
       </c>
       <c r="Q23" t="n">
-        <v>-99</v>
+        <v>4985</v>
       </c>
       <c r="R23" t="n">
-        <v>-296</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-197</v>
+        <v>4971</v>
       </c>
       <c r="T23" t="n">
-        <v>-98</v>
+        <v>4971</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4979</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Payments For Financed Property Plant And Equipment And Intangible Assets Financing Activities</t>
+          <t>Proceeds from Stock Plans</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>-33</v>
+        <v>515</v>
       </c>
       <c r="C24" t="n">
-        <v>-97</v>
+        <v>515</v>
       </c>
       <c r="D24" t="n">
-        <v>-73</v>
+        <v>643</v>
       </c>
       <c r="E24" t="n">
-        <v>-52</v>
+        <v>370</v>
       </c>
       <c r="F24" t="n">
-        <v>-97</v>
+        <v>370</v>
       </c>
       <c r="G24" t="n">
-        <v>-69</v>
+        <v>489</v>
       </c>
       <c r="H24" t="n">
-        <v>-40</v>
+        <v>285</v>
       </c>
       <c r="I24" t="n">
-        <v>-44</v>
+        <v>285</v>
       </c>
       <c r="J24" t="n">
-        <v>-31</v>
+        <v>403</v>
       </c>
       <c r="K24" t="n">
-        <v>-20</v>
+        <v>247</v>
       </c>
       <c r="L24" t="n">
-        <v>-54</v>
+        <v>246</v>
       </c>
       <c r="M24" t="n">
-        <v>-36</v>
+        <v>349</v>
       </c>
       <c r="N24" t="n">
-        <v>-22</v>
+        <v>205</v>
       </c>
       <c r="O24" t="n">
-        <v>-62</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>-19</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>-372</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>-155</v>
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from (Payments for) Other Financing Activities</t>
+          <t>Payments for Repurchase of Common Stock</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-81</v>
+        <v>-39044</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>-19312</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>-36271</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>-23815</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>-14095</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-25895</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>-14898</v>
       </c>
       <c r="I25" t="n">
-        <v>-1</v>
+        <v>-7740</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-6874</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>-3067</v>
       </c>
       <c r="L25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1</v>
+        <v>-8826</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>-5341</v>
       </c>
       <c r="O25" t="n">
-        <v>-2</v>
+        <v>-1996</v>
       </c>
       <c r="P25" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>-3</v>
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Net Cash Provided by (Used in) Financing Activities</t>
+          <t>Payments of Dividends</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-21283</v>
+        <v>-6290</v>
       </c>
       <c r="C26" t="n">
-        <v>-42266</v>
+        <v>-243</v>
       </c>
       <c r="D26" t="n">
-        <v>-27386</v>
+        <v>-732</v>
       </c>
       <c r="E26" t="n">
-        <v>-15553</v>
+        <v>-488</v>
       </c>
       <c r="F26" t="n">
-        <v>-32410</v>
+        <v>-244</v>
       </c>
       <c r="G26" t="n">
-        <v>-19665</v>
+        <v>-589</v>
       </c>
       <c r="H26" t="n">
-        <v>-9345</v>
+        <v>-344</v>
       </c>
       <c r="I26" t="n">
-        <v>-10004</v>
+        <v>-98</v>
       </c>
       <c r="J26" t="n">
-        <v>-5479</v>
+        <v>-296</v>
       </c>
       <c r="K26" t="n">
-        <v>-380</v>
+        <v>-199</v>
       </c>
       <c r="L26" t="n">
-        <v>-9961</v>
+        <v>-99</v>
       </c>
       <c r="M26" t="n">
-        <v>-6208</v>
+        <v>-300</v>
       </c>
       <c r="N26" t="n">
-        <v>-2446</v>
+        <v>-200</v>
       </c>
       <c r="O26" t="n">
-        <v>2610</v>
+        <v>-100</v>
       </c>
       <c r="P26" t="n">
-        <v>4030</v>
+        <v>-298</v>
       </c>
       <c r="Q26" t="n">
-        <v>-471</v>
+        <v>-198</v>
       </c>
       <c r="R26" t="n">
-        <v>4146</v>
+        <v>-99</v>
       </c>
       <c r="S26" t="n">
-        <v>4447</v>
+        <v>-296</v>
       </c>
       <c r="T26" t="n">
-        <v>4744</v>
+        <v>-197</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-98</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Period Increase (Decrease), Including Exchange Rate Effect</t>
+          <t>Payment, Tax Withholding, Share-based Payment Arrangement</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2632</v>
+        <v>-4531</v>
       </c>
       <c r="C27" t="n">
-        <v>2897</v>
+        <v>-2129</v>
       </c>
       <c r="D27" t="n">
-        <v>3050</v>
+        <v>-5809</v>
       </c>
       <c r="E27" t="n">
-        <v>6645</v>
+        <v>-3380</v>
       </c>
       <c r="F27" t="n">
-        <v>1827</v>
+        <v>-1532</v>
       </c>
       <c r="G27" t="n">
-        <v>1291</v>
+        <v>-5068</v>
       </c>
       <c r="H27" t="n">
-        <v>307</v>
+        <v>-3389</v>
       </c>
       <c r="I27" t="n">
-        <v>2130</v>
+        <v>-1752</v>
       </c>
       <c r="J27" t="n">
-        <v>2493</v>
+        <v>-1942</v>
       </c>
       <c r="K27" t="n">
-        <v>1690</v>
+        <v>-1179</v>
       </c>
       <c r="L27" t="n">
-        <v>810</v>
+        <v>-507</v>
       </c>
       <c r="M27" t="n">
-        <v>1023</v>
+        <v>-1131</v>
       </c>
       <c r="N27" t="n">
-        <v>1897</v>
+        <v>-837</v>
       </c>
       <c r="O27" t="n">
-        <v>441</v>
+        <v>-532</v>
       </c>
       <c r="P27" t="n">
-        <v>4781</v>
+        <v>-1282</v>
       </c>
       <c r="Q27" t="n">
-        <v>131</v>
+        <v>-843</v>
       </c>
       <c r="R27" t="n">
-        <v>-8645</v>
+        <v>-477</v>
       </c>
       <c r="S27" t="n">
-        <v>-7622</v>
+        <v>-716</v>
       </c>
       <c r="T27" t="n">
-        <v>4598</v>
+        <v>-418</v>
+      </c>
+      <c r="U27" t="n">
+        <v>-222</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
+          <t>nvda_PaymentForDeferredConsiderationFinancingFinancingActivities</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>10605</v>
+        <v>-2944</v>
       </c>
       <c r="C28" t="n">
-        <v>8589</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>8589</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>8589</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>7280</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>7280</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>7280</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>3389</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>3389</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>3389</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>1990</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>1990</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>1990</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>847</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>847</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>847</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>10896</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>10896</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>10896</v>
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Proceeds From Sale Of Equity Securities FvNi</t>
+          <t>Payments For Financed Property Plant And Equipment And Intangible Assets Financing Activities</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>26</v>
+        <v>-92</v>
       </c>
       <c r="C29" t="n">
-        <v>72</v>
+        <v>-33</v>
       </c>
       <c r="D29" t="n">
-        <v>70</v>
+        <v>-97</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>-73</v>
       </c>
       <c r="F29" t="n">
-        <v>171</v>
+        <v>-52</v>
       </c>
       <c r="G29" t="n">
-        <v>105</v>
+        <v>-97</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>-69</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>-44</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>-31</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>-54</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>-36</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>-62</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>-372</v>
+      </c>
+      <c r="U29" t="n">
+        <v>-155</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Payments to Acquire Debt Securities, Available-for-sale</t>
+          <t>Proceeds from (Payments for) Other Financing Activities</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-8000</v>
+        <v>31</v>
       </c>
       <c r="C30" t="n">
-        <v>-20076</v>
+        <v>-81</v>
       </c>
       <c r="D30" t="n">
-        <v>-14358</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
-        <v>-6546</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>-19565</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>-15047</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-9303</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>-10688</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>-5343</v>
+        <v>-1</v>
       </c>
       <c r="K30" t="n">
-        <v>-2801</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>-9764</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>-7576</v>
+        <v>1</v>
       </c>
       <c r="N30" t="n">
-        <v>-3932</v>
+        <v>1</v>
       </c>
       <c r="O30" t="n">
-        <v>-16020</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>-9268</v>
+        <v>-2</v>
       </c>
       <c r="Q30" t="n">
-        <v>-4470</v>
+        <v>-2</v>
       </c>
       <c r="R30" t="n">
-        <v>-12840</v>
+        <v>-2</v>
       </c>
       <c r="S30" t="n">
-        <v>-8286</v>
+        <v>-3</v>
       </c>
       <c r="T30" t="n">
-        <v>-861</v>
+        <v>-3</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Payments To Acquire Equity Securities FvNi</t>
+          <t>Net Cash Provided by (Used in) Financing Activities</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-18582</v>
+        <v>-27459</v>
       </c>
       <c r="C31" t="n">
-        <v>-4702</v>
+        <v>-21283</v>
       </c>
       <c r="D31" t="n">
-        <v>-995</v>
+        <v>-42266</v>
       </c>
       <c r="E31" t="n">
-        <v>-649</v>
+        <v>-27386</v>
       </c>
       <c r="F31" t="n">
-        <v>-1008</v>
+        <v>-15553</v>
       </c>
       <c r="G31" t="n">
-        <v>534</v>
+        <v>-32410</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>-19665</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>-9345</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-10004</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>-5479</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>-380</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>-9961</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>-6208</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>-2446</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2610</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>4030</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>-471</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>4146</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>4447</v>
+      </c>
+      <c r="U31" t="n">
+        <v>4744</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Repayments of Debt</t>
+          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Period Increase (Decrease), Including Exchange Rate Effect</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0</v>
+        <v>11838</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>2632</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>2897</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>3050</v>
       </c>
       <c r="F32" t="n">
-        <v>-1250</v>
+        <v>6645</v>
       </c>
       <c r="G32" t="n">
-        <v>-1250</v>
+        <v>1827</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>1291</v>
       </c>
       <c r="I32" t="n">
-        <v>-1250</v>
+        <v>307</v>
       </c>
       <c r="J32" t="n">
-        <v>-1250</v>
+        <v>2130</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>2493</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1690</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>810</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="O32" t="n">
-        <v>-1000</v>
+        <v>1897</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>441</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4781</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>-8645</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>-7622</v>
+      </c>
+      <c r="U32" t="n">
+        <v>4598</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Income Taxes Paid, Net</t>
+          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0</v>
+        <v>10605</v>
       </c>
       <c r="C33" t="n">
-        <v>13309</v>
+        <v>10605</v>
       </c>
       <c r="D33" t="n">
-        <v>8451</v>
+        <v>8589</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>8589</v>
       </c>
       <c r="F33" t="n">
-        <v>10989</v>
+        <v>8589</v>
       </c>
       <c r="G33" t="n">
-        <v>7449</v>
+        <v>7280</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>7280</v>
       </c>
       <c r="I33" t="n">
-        <v>4676</v>
+        <v>7280</v>
       </c>
       <c r="J33" t="n">
-        <v>328</v>
+        <v>3389</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>3389</v>
       </c>
       <c r="L33" t="n">
-        <v>1372</v>
+        <v>3389</v>
       </c>
       <c r="M33" t="n">
-        <v>1108</v>
+        <v>1990</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>1990</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>1990</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>847</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>847</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>847</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>10896</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>10896</v>
+      </c>
+      <c r="U33" t="n">
+        <v>10896</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Payments for (Proceeds from) Other Investing Activities</t>
+          <t>Proceeds from Maturities, Prepayments and Calls of Debt Securities, Available-for-sale</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>0</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>1946</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
+        <v>8980</v>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>6252</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>3122</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>9485</v>
       </c>
       <c r="H34" t="n">
-        <v>-135</v>
+        <v>8098</v>
       </c>
       <c r="I34" t="n">
-        <v>-872</v>
+        <v>4004</v>
       </c>
       <c r="J34" t="n">
-        <v>-435</v>
+        <v>8001</v>
       </c>
       <c r="K34" t="n">
-        <v>-221</v>
+        <v>5111</v>
       </c>
       <c r="L34" t="n">
-        <v>-83</v>
+        <v>2512</v>
       </c>
       <c r="M34" t="n">
-        <v>-65</v>
+        <v>16792</v>
       </c>
       <c r="N34" t="n">
-        <v>-35</v>
+        <v>10983</v>
       </c>
       <c r="O34" t="n">
-        <v>-14</v>
+        <v>5947</v>
       </c>
       <c r="P34" t="n">
-        <v>3</v>
+        <v>7780</v>
       </c>
       <c r="Q34" t="n">
-        <v>-2</v>
+        <v>5236</v>
       </c>
       <c r="R34" t="n">
-        <v>-4</v>
+        <v>3140</v>
       </c>
       <c r="S34" t="n">
-        <v>-7</v>
+        <v>5165</v>
       </c>
       <c r="T34" t="n">
-        <v>-6</v>
+        <v>1032</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Business Combination Advanced Consideration Written Off</t>
+          <t>Proceeds from Sale of Debt Securities, Available-for-sale</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>0</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
+        <v>487</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>487</v>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="I35" t="n">
-        <v>0</v>
+        <v>149</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -5927,59 +6182,62 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>1353</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>1353</v>
+        <v>1806</v>
       </c>
       <c r="N35" t="n">
-        <v>1353</v>
+        <v>1731</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1029</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>916</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>705</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>358</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>502</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>259</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Debt, Net of Issuance Costs</t>
+          <t>Proceeds From Sale Of Equity Securities FvNi</t>
         </is>
       </c>
       <c r="B36" t="n">
         <v>0</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="F36" t="n">
         <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="I36" t="n">
         <v>0</v>
@@ -6000,85 +6258,359 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>4977</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>4985</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>4971</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>4971</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>4979</v>
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>Payments To Acquire Equity Securities FvNi</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-18582</v>
+      </c>
+      <c r="D37" t="n">
+        <v>-4702</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-995</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-649</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-1008</v>
+      </c>
+      <c r="H37" t="n">
+        <v>534</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Repayments of Debt</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-1250</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-1250</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" t="n">
+        <v>-1250</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-1250</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>-1000</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Income Taxes Paid, Net</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" t="n">
+        <v>13309</v>
+      </c>
+      <c r="E39" t="n">
+        <v>8451</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" t="n">
+        <v>10989</v>
+      </c>
+      <c r="H39" t="n">
+        <v>7449</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" t="n">
+        <v>4676</v>
+      </c>
+      <c r="K39" t="n">
+        <v>328</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
+        <v>1372</v>
+      </c>
+      <c r="N39" t="n">
+        <v>1108</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Business Combination Advanced Consideration Written Off</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
+        <v>1353</v>
+      </c>
+      <c r="N40" t="n">
+        <v>1353</v>
+      </c>
+      <c r="O40" t="n">
+        <v>1353</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
           <t>Liabilities Assumed</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>0</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" t="n">
-        <v>0</v>
-      </c>
-      <c r="P37" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="n">
+      <c r="B41" t="n">
+        <v>0</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
         <v>257</v>
       </c>
-      <c r="T37" t="n">
+      <c r="U41" t="n">
         <v>230</v>
       </c>
     </row>
@@ -6093,65 +6625,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:U2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46229</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46138</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45956</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45865</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45774</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45592</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45501</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45410</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45228</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45137</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45046</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44864</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44773</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44682</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44500</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44409</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44318</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44129</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44038</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43947</v>
       </c>
     </row>
@@ -6162,60 +6697,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>509</v>
+      </c>
+      <c r="C2" t="n">
         <v>466</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>341</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>301</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>300</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>273</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>250</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>246</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>230</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>208</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>187</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>156</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>145</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>147</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>140</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>132</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>135</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>116</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>124</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>100</v>
       </c>
     </row>
